--- a/Data/FlightPlan/FPL_15OCT26.xlsx
+++ b/Data/FlightPlan/FPL_15OCT26.xlsx
@@ -422,732 +422,759 @@
     <t>10:35</t>
   </si>
   <si>
+    <t>11:06</t>
+  </si>
+  <si>
     <t>11:05</t>
   </si>
   <si>
     <t>12:20</t>
   </si>
   <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>VN-A532</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>15:22</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>07:06</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>19:25</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>09:04</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>09:02</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>11:29</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>13:03</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>00:40</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>13:49</t>
+  </si>
+  <si>
+    <t>HYD</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>16:07</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>03:35</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>08:26</t>
+  </si>
+  <si>
+    <t>10:46</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:45</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>09:07</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
     <t>13:15</t>
   </si>
   <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>18:40</t>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>08:06</t>
+  </si>
+  <si>
+    <t>10:14</t>
   </si>
   <si>
     <t>20:30</t>
   </si>
   <si>
-    <t>22:25</t>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>12:49</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>09:14</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>11:17</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>07:57</t>
+  </si>
+  <si>
+    <t>09:24</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>09:43</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>07:37</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>11:32</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>08:19</t>
+  </si>
+  <si>
+    <t>11:13</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>09:46</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>11:09</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>11:57</t>
+  </si>
+  <si>
+    <t>ENH</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>06:39</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>08:49</t>
+  </si>
+  <si>
+    <t>10:41</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>13:44</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>07:49</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>HIJ</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>12:39</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>13:55</t>
   </si>
   <si>
     <t>21:05</t>
   </si>
   <si>
-    <t>VN-A532</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>07:06</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>19:25</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>09:04</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>09:02</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>13:03</t>
-  </si>
-  <si>
-    <t>14:35</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>00:40</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>17:25</t>
-  </si>
-  <si>
-    <t>HYD</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>03:35</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>08:26</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>11:06</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:45</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>09:07</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>08:06</t>
-  </si>
-  <si>
-    <t>10:14</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>09:14</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>07:57</t>
-  </si>
-  <si>
-    <t>09:24</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>09:43</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>07:37</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>11:32</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>08:19</t>
-  </si>
-  <si>
-    <t>10:56</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>09:46</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>ENH</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>06:39</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>08:49</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>13:44</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>07:49</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>HIJ</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>12:39</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
     <t>VN-A668</t>
   </si>
   <si>
@@ -1205,6 +1232,9 @@
     <t>09:42</t>
   </si>
   <si>
+    <t>11:49</t>
+  </si>
+  <si>
     <t>15:10</t>
   </si>
   <si>
@@ -1214,6 +1244,9 @@
     <t>07:15</t>
   </si>
   <si>
+    <t>11:36</t>
+  </si>
+  <si>
     <t>MFM</t>
   </si>
   <si>
@@ -1238,6 +1271,9 @@
     <t>09:11</t>
   </si>
   <si>
+    <t>11:19</t>
+  </si>
+  <si>
     <t>11:45</t>
   </si>
   <si>
@@ -1256,6 +1292,9 @@
     <t>VN-A687</t>
   </si>
   <si>
+    <t>11:43</t>
+  </si>
+  <si>
     <t>15:35</t>
   </si>
   <si>
@@ -1265,6 +1304,9 @@
     <t>08:14</t>
   </si>
   <si>
+    <t>10:31</t>
+  </si>
+  <si>
     <t>VN-A693</t>
   </si>
   <si>
@@ -1289,9 +1331,6 @@
     <t>08:47</t>
   </si>
   <si>
-    <t>10:54</t>
-  </si>
-  <si>
     <t>18:35</t>
   </si>
   <si>
@@ -1349,7 +1388,7 @@
     <t>Total Record(s): 354</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 15, 2026 09:08</t>
+    <t xml:space="preserve">Generated on  Oct 15, 2026 10:11</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3436,7 +3475,9 @@
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
-      <c r="M58" s="7"/>
+      <c t="s" r="M58" s="7">
+        <v>137</v>
+      </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c t="s" r="A59" s="6">
@@ -3462,14 +3503,18 @@
         <v>23</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>138</v>
-      </c>
-      <c r="K59" s="7"/>
+        <v>139</v>
+      </c>
+      <c t="s" r="K59" s="7">
+        <v>96</v>
+      </c>
       <c r="L59" s="7"/>
-      <c r="M59" s="7"/>
+      <c t="s" r="M59" s="7">
+        <v>19</v>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c t="s" r="A60" s="6">
@@ -3501,11 +3546,11 @@
         <v>114</v>
       </c>
       <c t="s" r="K60" s="7">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="L60" s="7"/>
       <c t="s" r="M60" s="7">
-        <v>140</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
@@ -3535,14 +3580,14 @@
         <v>116</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="K61" s="7">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="L61" s="7"/>
       <c t="s" r="M61" s="7">
-        <v>91</v>
+        <v>141</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
@@ -3575,11 +3620,11 @@
         <v>143</v>
       </c>
       <c t="s" r="K62" s="7">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="L62" s="7"/>
       <c t="s" r="M62" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
@@ -3609,14 +3654,14 @@
         <v>103</v>
       </c>
       <c t="s" r="J63" s="7">
+        <v>145</v>
+      </c>
+      <c t="s" r="K63" s="7">
         <v>146</v>
-      </c>
-      <c t="s" r="K63" s="7">
-        <v>147</v>
       </c>
       <c r="L63" s="7"/>
       <c t="s" r="M63" s="7">
-        <v>55</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
@@ -3727,7 +3772,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3757,10 +3802,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I68" s="7">
+        <v>151</v>
+      </c>
+      <c t="s" r="J68" s="7">
         <v>152</v>
-      </c>
-      <c t="s" r="J68" s="7">
-        <v>153</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3793,7 +3838,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -3805,7 +3850,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="J70" s="7">
         <v>111</v>
@@ -3828,7 +3873,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -3843,11 +3888,13 @@
         <v>132</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
-      <c r="M71" s="7"/>
+      <c t="s" r="M71" s="7">
+        <v>156</v>
+      </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c t="s" r="A72" s="6">
@@ -3861,7 +3908,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3878,23 +3925,27 @@
       <c t="s" r="J72" s="7">
         <v>158</v>
       </c>
-      <c r="K72" s="7"/>
+      <c t="s" r="K72" s="7">
+        <v>159</v>
+      </c>
       <c r="L72" s="7"/>
-      <c r="M72" s="7"/>
+      <c t="s" r="M72" s="7">
+        <v>160</v>
+      </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c t="s" r="A73" s="6">
         <v>13</v>
       </c>
       <c r="B73" s="7">
-        <v>214</v>
+        <v>140</v>
       </c>
       <c t="s" r="C73" s="7">
         <v>14</v>
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3903,13 +3954,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H73" s="8">
-        <v>159</v>
+        <v>23</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3920,29 +3971,29 @@
         <v>13</v>
       </c>
       <c r="B74" s="7">
-        <v>213</v>
+        <v>151</v>
       </c>
       <c t="s" r="C74" s="7">
         <v>14</v>
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G74" s="8">
-        <v>159</v>
+        <v>23</v>
       </c>
       <c t="s" r="H74" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -3960,7 +4011,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -3972,10 +4023,10 @@
         <v>95</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -3993,7 +4044,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -4008,7 +4059,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -4041,7 +4092,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4050,17 +4101,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H78" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
-      <c r="M78" s="7"/>
+      <c t="s" r="M78" s="7">
+        <v>19</v>
+      </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c t="s" r="A79" s="6">
@@ -4074,13 +4127,13 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G79" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="H79" s="8">
         <v>31</v>
@@ -4089,7 +4142,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -4107,7 +4160,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4116,13 +4169,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -4140,19 +4193,19 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="J81" s="7">
         <v>103</v>
@@ -4173,7 +4226,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4182,13 +4235,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H82" s="8">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4206,22 +4259,22 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G83" s="8">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c t="s" r="H83" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4254,7 +4307,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4273,7 +4326,9 @@
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
-      <c r="M85" s="7"/>
+      <c t="s" r="M85" s="7">
+        <v>179</v>
+      </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c t="s" r="A86" s="6">
@@ -4287,7 +4342,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4302,7 +4357,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4320,7 +4375,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4329,13 +4384,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H87" s="8">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4353,13 +4408,13 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G88" s="8">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c t="s" r="H88" s="8">
         <v>23</v>
@@ -4368,7 +4423,7 @@
         <v>82</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4401,7 +4456,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4413,15 +4468,15 @@
         <v>23</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
       <c t="s" r="M90" s="7">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -4436,7 +4491,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4445,10 +4500,10 @@
         <v>23</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c t="s" r="J91" s="7">
         <v>60</v>
@@ -4471,13 +4526,13 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>23</v>
@@ -4504,7 +4559,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4516,10 +4571,10 @@
         <v>95</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>189</v>
+        <v>144</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4537,7 +4592,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4549,7 +4604,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J94" s="7">
         <v>117</v>
@@ -4570,7 +4625,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4582,10 +4637,10 @@
         <v>83</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4618,7 +4673,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4630,15 +4685,15 @@
         <v>23</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -4653,7 +4708,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4662,13 +4717,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="I98" s="7">
         <v>157</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4686,22 +4741,22 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="H99" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4719,7 +4774,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4728,13 +4783,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H100" s="8">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4752,22 +4807,22 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G101" s="8">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="H101" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4800,7 +4855,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4812,7 +4867,7 @@
         <v>149</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="J103" s="7">
         <v>132</v>
@@ -4820,7 +4875,7 @@
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
       <c t="s" r="M103" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
@@ -4835,7 +4890,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4850,11 +4905,13 @@
         <v>135</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
-      <c r="M104" s="7"/>
+      <c t="s" r="M104" s="7">
+        <v>207</v>
+      </c>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c t="s" r="A105" s="6">
@@ -4868,7 +4925,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4880,10 +4937,10 @@
         <v>73</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4901,7 +4958,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4913,7 +4970,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J106" s="7">
         <v>28</v>
@@ -4949,7 +5006,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4961,14 +5018,16 @@
         <v>23</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c t="s" r="J108" s="7">
         <v>33</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
-      <c r="M108" s="7"/>
+      <c t="s" r="M108" s="7">
+        <v>209</v>
+      </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
       <c t="s" r="A109" s="6">
@@ -4982,7 +5041,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -4994,28 +5053,32 @@
         <v>16</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J109" s="7">
         <v>36</v>
       </c>
-      <c r="K109" s="7"/>
+      <c t="s" r="K109" s="7">
+        <v>198</v>
+      </c>
       <c r="L109" s="7"/>
-      <c r="M109" s="7"/>
+      <c t="s" r="M109" s="7">
+        <v>90</v>
+      </c>
     </row>
     <row r="110" ht="15" customHeight="1">
       <c t="s" r="A110" s="6">
         <v>13</v>
       </c>
       <c r="B110" s="7">
-        <v>140</v>
+        <v>214</v>
       </c>
       <c t="s" r="C110" s="7">
         <v>14</v>
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5024,50 +5087,58 @@
         <v>16</v>
       </c>
       <c t="s" r="H110" s="8">
-        <v>23</v>
+        <v>210</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>39</v>
-      </c>
-      <c r="K110" s="7"/>
+        <v>38</v>
+      </c>
+      <c t="s" r="K110" s="7">
+        <v>211</v>
+      </c>
       <c r="L110" s="7"/>
-      <c r="M110" s="7"/>
+      <c t="s" r="M110" s="7">
+        <v>22</v>
+      </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
       <c t="s" r="A111" s="6">
         <v>13</v>
       </c>
       <c r="B111" s="7">
-        <v>151</v>
+        <v>213</v>
       </c>
       <c t="s" r="C111" s="7">
         <v>14</v>
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G111" s="8">
-        <v>23</v>
+        <v>210</v>
       </c>
       <c t="s" r="H111" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>70</v>
-      </c>
-      <c r="K111" s="7"/>
+        <v>40</v>
+      </c>
+      <c t="s" r="K111" s="7">
+        <v>212</v>
+      </c>
       <c r="L111" s="7"/>
-      <c r="M111" s="7"/>
+      <c t="s" r="M111" s="7">
+        <v>202</v>
+      </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
       <c t="s" r="A112" s="6">
@@ -5081,7 +5152,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5093,10 +5164,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -5114,7 +5185,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5126,7 +5197,7 @@
         <v>123</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c t="s" r="J113" s="7">
         <v>29</v>
@@ -5162,7 +5233,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5174,7 +5245,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="J115" s="7">
         <v>110</v>
@@ -5197,7 +5268,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5209,7 +5280,7 @@
         <v>89</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c t="s" r="J116" s="7">
         <v>20</v>
@@ -5232,7 +5303,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5244,7 +5315,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>208</v>
+        <v>161</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>22</v>
@@ -5265,7 +5336,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5277,7 +5348,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c t="s" r="J118" s="7">
         <v>128</v>
@@ -5298,7 +5369,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5310,10 +5381,10 @@
         <v>73</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5346,7 +5417,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5358,15 +5429,15 @@
         <v>31</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
       <c t="s" r="M121" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -5381,7 +5452,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5390,10 +5461,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>222</v>
+        <v>160</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>79</v>
@@ -5414,13 +5485,13 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>31</v>
@@ -5429,7 +5500,7 @@
         <v>102</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>144</v>
+        <v>226</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5447,7 +5518,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5462,7 +5533,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5480,7 +5551,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5492,10 +5563,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5528,7 +5599,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5543,7 +5614,7 @@
         <v>135</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5563,7 +5634,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5578,7 +5649,7 @@
         <v>126</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5596,7 +5667,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5608,7 +5679,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c t="s" r="J129" s="7">
         <v>91</v>
@@ -5629,7 +5700,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5641,7 +5712,7 @@
         <v>95</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c t="s" r="J130" s="7">
         <v>25</v>
@@ -5662,7 +5733,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5674,10 +5745,10 @@
         <v>73</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5710,27 +5781,27 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c t="s" r="H133" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
@@ -5745,7 +5816,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5760,7 +5831,7 @@
         <v>97</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5778,7 +5849,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5790,7 +5861,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c t="s" r="J135" s="7">
         <v>56</v>
@@ -5811,7 +5882,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5823,7 +5894,7 @@
         <v>107</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>29</v>
@@ -5859,7 +5930,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5878,7 +5949,9 @@
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
-      <c r="M138" s="7"/>
+      <c t="s" r="M138" s="7">
+        <v>240</v>
+      </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
       <c t="s" r="A139" s="6">
@@ -5892,7 +5965,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5904,10 +5977,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5925,7 +5998,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5934,10 +6007,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c t="s" r="J140" s="7">
         <v>117</v>
@@ -5958,22 +6031,22 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -6006,7 +6079,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6021,14 +6094,14 @@
         <v>111</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="K143" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6043,7 +6116,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6076,7 +6149,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6091,7 +6164,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -6109,7 +6182,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6121,7 +6194,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="J146" s="7">
         <v>119</v>
@@ -6157,13 +6230,13 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>16</v>
@@ -6172,11 +6245,13 @@
         <v>136</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
-      <c r="M148" s="7"/>
+      <c t="s" r="M148" s="7">
+        <v>251</v>
+      </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
       <c t="s" r="A149" s="6">
@@ -6190,7 +6265,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6223,7 +6298,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6235,10 +6310,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6256,7 +6331,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6268,7 +6343,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c t="s" r="J151" s="7">
         <v>18</v>
@@ -6304,7 +6379,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6316,14 +6391,16 @@
         <v>23</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J153" s="7">
         <v>88</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
-      <c r="M153" s="7"/>
+      <c t="s" r="M153" s="7">
+        <v>169</v>
+      </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
       <c t="s" r="A154" s="6">
@@ -6337,7 +6414,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6349,10 +6426,10 @@
         <v>45</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6370,7 +6447,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6382,7 +6459,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>103</v>
@@ -6418,7 +6495,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6430,7 +6507,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c t="s" r="J157" s="7">
         <v>35</v>
@@ -6451,7 +6528,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6463,7 +6540,7 @@
         <v>95</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c t="s" r="J158" s="7">
         <v>60</v>
@@ -6484,7 +6561,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6496,7 +6573,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>208</v>
+        <v>161</v>
       </c>
       <c t="s" r="J159" s="7">
         <v>79</v>
@@ -6517,7 +6594,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6529,7 +6606,7 @@
         <v>95</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c t="s" r="J160" s="7">
         <v>142</v>
@@ -6550,7 +6627,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6559,13 +6636,13 @@
         <v>95</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6583,22 +6660,22 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c t="s" r="H162" s="8">
         <v>95</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6631,7 +6708,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6643,7 +6720,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c t="s" r="J164" s="7">
         <v>119</v>
@@ -6651,7 +6728,7 @@
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -6666,7 +6743,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6678,14 +6755,16 @@
         <v>95</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
-      <c r="M165" s="7"/>
+      <c t="s" r="M165" s="7">
+        <v>266</v>
+      </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
       <c t="s" r="A166" s="6">
@@ -6699,7 +6778,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6714,7 +6793,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6732,7 +6811,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6747,7 +6826,7 @@
         <v>60</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6765,7 +6844,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6780,7 +6859,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6798,7 +6877,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6813,7 +6892,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6831,7 +6910,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6843,7 +6922,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="J170" s="7">
         <v>55</v>
@@ -6879,7 +6958,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6888,18 +6967,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
-        <v>265</v>
+        <v>137</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
@@ -6914,19 +6993,19 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>95</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c t="s" r="J173" s="7">
         <v>20</v>
@@ -6947,7 +7026,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6962,7 +7041,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6980,7 +7059,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6989,13 +7068,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -7013,22 +7092,22 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7046,7 +7125,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7058,10 +7137,10 @@
         <v>94</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7079,7 +7158,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7091,10 +7170,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7127,7 +7206,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7147,7 +7226,7 @@
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7162,7 +7241,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7177,11 +7256,13 @@
         <v>135</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
-      <c r="M181" s="7"/>
+      <c t="s" r="M181" s="7">
+        <v>207</v>
+      </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
       <c t="s" r="A182" s="6">
@@ -7195,7 +7276,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7207,14 +7288,18 @@
         <v>95</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>274</v>
-      </c>
-      <c r="K182" s="7"/>
+        <v>279</v>
+      </c>
+      <c t="s" r="K182" s="7">
+        <v>96</v>
+      </c>
       <c r="L182" s="7"/>
-      <c r="M182" s="7"/>
+      <c t="s" r="M182" s="7">
+        <v>19</v>
+      </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
       <c t="s" r="A183" s="6">
@@ -7228,7 +7313,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7240,14 +7325,18 @@
         <v>23</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>139</v>
+        <v>280</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>232</v>
-      </c>
-      <c r="K183" s="7"/>
+        <v>236</v>
+      </c>
+      <c t="s" r="K183" s="7">
+        <v>36</v>
+      </c>
       <c r="L183" s="7"/>
-      <c r="M183" s="7"/>
+      <c t="s" r="M183" s="7">
+        <v>50</v>
+      </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
       <c t="s" r="A184" s="6">
@@ -7261,7 +7350,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7276,7 +7365,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7294,7 +7383,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7327,7 +7416,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7339,10 +7428,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7375,7 +7464,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7384,10 +7473,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c t="s" r="J188" s="7">
         <v>111</v>
@@ -7395,7 +7484,7 @@
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -7410,27 +7499,27 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c t="s" r="H189" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -7445,7 +7534,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7457,10 +7546,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7478,7 +7567,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7511,7 +7600,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7544,7 +7633,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7559,7 +7648,7 @@
         <v>63</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7577,7 +7666,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7586,13 +7675,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>144</v>
+        <v>226</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>145</v>
+        <v>287</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7610,22 +7699,22 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c t="s" r="H195" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7658,7 +7747,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7667,17 +7756,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c t="s" r="I197" s="7">
         <v>59</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
-      <c r="M197" s="7"/>
+      <c t="s" r="M197" s="7">
+        <v>293</v>
+      </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
       <c t="s" r="A198" s="6">
@@ -7691,13 +7782,13 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>16</v>
@@ -7706,7 +7797,7 @@
         <v>88</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7724,7 +7815,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7736,10 +7827,10 @@
         <v>94</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7757,7 +7848,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7769,10 +7860,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7805,7 +7896,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7820,12 +7911,12 @@
         <v>75</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -7840,7 +7931,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7859,7 +7950,9 @@
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
-      <c r="M203" s="7"/>
+      <c t="s" r="M203" s="7">
+        <v>160</v>
+      </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
       <c t="s" r="A204" s="6">
@@ -7873,7 +7966,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7906,7 +7999,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7921,7 +8014,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7939,7 +8032,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7951,10 +8044,10 @@
         <v>95</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7972,7 +8065,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7984,7 +8077,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c t="s" r="J207" s="7">
         <v>92</v>
@@ -8005,7 +8098,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8014,13 +8107,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -8038,22 +8131,22 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -8086,7 +8179,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8098,7 +8191,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c t="s" r="J211" s="7">
         <v>111</v>
@@ -8106,7 +8199,7 @@
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>295</v>
+        <v>303</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8121,7 +8214,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8133,14 +8226,16 @@
         <v>94</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>296</v>
+        <v>159</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
-      <c r="M212" s="7"/>
+      <c t="s" r="M212" s="7">
+        <v>304</v>
+      </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
       <c t="s" r="A213" s="6">
@@ -8154,7 +8249,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8187,7 +8282,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8199,10 +8294,10 @@
         <v>134</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8220,7 +8315,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8268,7 +8363,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8283,7 +8378,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8316,7 +8411,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8325,10 +8420,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c t="s" r="J219" s="7">
         <v>43</v>
@@ -8336,7 +8431,7 @@
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>300</v>
+        <v>308</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -8351,19 +8446,19 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c t="s" r="H220" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c t="s" r="J220" s="7">
         <v>59</v>
@@ -8371,7 +8466,7 @@
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>301</v>
+        <v>309</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -8386,7 +8481,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8398,7 +8493,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>296</v>
+        <v>159</v>
       </c>
       <c t="s" r="J221" s="7">
         <v>60</v>
@@ -8419,7 +8514,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8434,7 +8529,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8452,7 +8547,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8464,10 +8559,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8485,7 +8580,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8500,7 +8595,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8518,7 +8613,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8530,10 +8625,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>145</v>
+        <v>287</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8551,7 +8646,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8563,10 +8658,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8599,7 +8694,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8608,13 +8703,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>139</v>
+        <v>280</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8632,22 +8727,22 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8665,7 +8760,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8674,7 +8769,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="I230" s="7">
         <v>40</v>
@@ -8698,13 +8793,13 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="H231" s="8">
         <v>16</v>
@@ -8713,7 +8808,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8746,7 +8841,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8761,12 +8856,12 @@
         <v>46</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>311</v>
+        <v>319</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -8781,7 +8876,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8790,10 +8885,10 @@
         <v>23</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>60</v>
@@ -8814,13 +8909,13 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>23</v>
@@ -8847,7 +8942,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8862,7 +8957,7 @@
         <v>127</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8880,7 +8975,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8892,10 +8987,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8928,7 +9023,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8940,7 +9035,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>19</v>
@@ -8948,7 +9043,7 @@
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -8963,7 +9058,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8972,13 +9067,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H240" s="8">
+        <v>249</v>
+      </c>
+      <c t="s" r="I240" s="7">
+        <v>247</v>
+      </c>
+      <c t="s" r="J240" s="7">
         <v>245</v>
-      </c>
-      <c t="s" r="I240" s="7">
-        <v>243</v>
-      </c>
-      <c t="s" r="J240" s="7">
-        <v>241</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -9011,7 +9106,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9023,7 +9118,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>109</v>
@@ -9031,7 +9126,7 @@
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9046,7 +9141,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9055,17 +9150,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c t="s" r="I243" s="7">
         <v>76</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
-      <c r="M243" s="7"/>
+      <c t="s" r="M243" s="7">
+        <v>97</v>
+      </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
       <c t="s" r="A244" s="6">
@@ -9079,13 +9176,13 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c t="s" r="H244" s="8">
         <v>16</v>
@@ -9094,7 +9191,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9112,7 +9209,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9127,7 +9224,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9160,7 +9257,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9175,12 +9272,12 @@
         <v>111</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>317</v>
+        <v>325</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -9195,7 +9292,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9207,7 +9304,7 @@
         <v>95</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>222</v>
+        <v>160</v>
       </c>
       <c t="s" r="J248" s="7">
         <v>36</v>
@@ -9228,7 +9325,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9261,7 +9358,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9273,10 +9370,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9294,7 +9391,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9306,10 +9403,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9327,7 +9424,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9339,7 +9436,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c t="s" r="J252" s="7">
         <v>18</v>
@@ -9375,7 +9472,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9387,10 +9484,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9408,7 +9505,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9420,10 +9517,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>144</v>
+        <v>226</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9441,7 +9538,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9453,10 +9550,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9474,7 +9571,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9483,7 +9580,7 @@
         <v>23</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c t="s" r="I257" s="7">
         <v>118</v>
@@ -9522,7 +9619,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="F259" s="7">
         <v>320</v>
@@ -9534,15 +9631,15 @@
         <v>23</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -9557,7 +9654,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="F260" s="7">
         <v>320</v>
@@ -9577,7 +9674,7 @@
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -9592,7 +9689,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="F261" s="7">
         <v>320</v>
@@ -9601,13 +9698,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c t="s" r="I261" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9625,22 +9722,22 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="F262" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9658,7 +9755,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="F263" s="7">
         <v>320</v>
@@ -9667,13 +9764,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9691,13 +9788,13 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>16</v>
@@ -9706,7 +9803,7 @@
         <v>142</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9739,7 +9836,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9748,10 +9845,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c t="s" r="J266" s="7">
         <v>76</v>
@@ -9759,7 +9856,7 @@
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -9774,26 +9871,28 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
-      <c r="M267" s="7"/>
+      <c t="s" r="M267" s="7">
+        <v>345</v>
+      </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
       <c t="s" r="A268" s="6">
@@ -9807,7 +9906,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9819,7 +9918,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>90</v>
@@ -9840,7 +9939,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9852,10 +9951,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>337</v>
+        <v>211</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9873,7 +9972,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9888,7 +9987,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9906,7 +10005,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9918,10 +10017,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>340</v>
+        <v>146</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9954,7 +10053,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -9963,13 +10062,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9987,22 +10086,22 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -10035,7 +10134,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
@@ -10050,12 +10149,12 @@
         <v>130</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
@@ -10070,7 +10169,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
@@ -10082,14 +10181,16 @@
         <v>23</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
-      <c r="M277" s="7"/>
+      <c t="s" r="M277" s="7">
+        <v>356</v>
+      </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
       <c t="s" r="A278" s="6">
@@ -10103,7 +10204,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
@@ -10112,13 +10213,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c t="s" r="I278" s="7">
         <v>21</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10136,13 +10237,13 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>23</v>
@@ -10151,7 +10252,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10169,7 +10270,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -10181,10 +10282,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10217,7 +10318,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10226,18 +10327,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -10252,19 +10353,19 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>32</v>
@@ -10272,7 +10373,7 @@
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>354</v>
+        <v>362</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -10287,26 +10388,28 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
-      <c r="M284" s="7"/>
+      <c t="s" r="M284" s="7">
+        <v>363</v>
+      </c>
     </row>
     <row r="285" ht="15" customHeight="1">
       <c t="s" r="A285" s="6">
@@ -10320,19 +10423,19 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>60</v>
@@ -10353,7 +10456,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10386,7 +10489,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10398,7 +10501,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>40</v>
@@ -10419,7 +10522,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10431,7 +10534,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>92</v>
@@ -10452,7 +10555,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10464,10 +10567,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I289" s="7">
+        <v>246</v>
+      </c>
+      <c t="s" r="J289" s="7">
         <v>242</v>
-      </c>
-      <c t="s" r="J289" s="7">
-        <v>238</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10500,13 +10603,13 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c t="s" r="H291" s="8">
         <v>23</v>
@@ -10520,7 +10623,7 @@
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>358</v>
+        <v>367</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -10535,7 +10638,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -10544,13 +10647,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c t="s" r="I292" s="7">
         <v>114</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10568,22 +10671,22 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10601,7 +10704,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10610,13 +10713,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10634,13 +10737,13 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>23</v>
@@ -10649,7 +10752,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10682,7 +10785,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
@@ -10694,7 +10797,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c t="s" r="J297" s="7">
         <v>46</v>
@@ -10702,7 +10805,7 @@
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>363</v>
+        <v>372</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -10717,7 +10820,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -10732,12 +10835,12 @@
         <v>29</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>365</v>
+        <v>156</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -10752,7 +10855,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -10764,17 +10867,17 @@
         <v>95</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="K299" s="7">
-        <v>296</v>
+        <v>159</v>
       </c>
       <c r="L299" s="7"/>
       <c t="s" r="M299" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1">
@@ -10789,7 +10892,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -10798,7 +10901,7 @@
         <v>95</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="I300" s="7">
         <v>20</v>
@@ -10822,19 +10925,19 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>70</v>
@@ -10855,7 +10958,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -10864,13 +10967,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10888,22 +10991,22 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -10936,7 +11039,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -10945,18 +11048,18 @@
         <v>23</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -10971,13 +11074,13 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>23</v>
@@ -10986,7 +11089,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -11004,7 +11107,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -11016,7 +11119,7 @@
         <v>95</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c t="s" r="J307" s="7">
         <v>143</v>
@@ -11037,7 +11140,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11049,10 +11152,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>189</v>
+        <v>144</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -11085,7 +11188,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -11097,15 +11200,15 @@
         <v>23</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11120,7 +11223,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -11129,17 +11232,19 @@
         <v>23</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="I311" s="7">
         <v>76</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
-      <c r="M311" s="7"/>
+      <c t="s" r="M311" s="7">
+        <v>267</v>
+      </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
       <c t="s" r="A312" s="6">
@@ -11153,13 +11258,13 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>23</v>
@@ -11168,7 +11273,7 @@
         <v>100</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11186,7 +11291,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11201,7 +11306,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>147</v>
+        <v>387</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11234,7 +11339,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11246,7 +11351,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J315" s="7">
         <v>36</v>
@@ -11267,7 +11372,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11279,10 +11384,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11300,7 +11405,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11309,10 +11414,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>56</v>
@@ -11333,22 +11438,22 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11381,7 +11486,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11390,18 +11495,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>381</v>
+        <v>390</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -11416,13 +11521,13 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>16</v>
@@ -11449,7 +11554,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11461,10 +11566,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11482,7 +11587,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11494,7 +11599,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>102</v>
@@ -11515,7 +11620,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11524,13 +11629,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c t="s" r="I324" s="7">
         <v>142</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11548,22 +11653,22 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11589,14 +11694,14 @@
         <v>26</v>
       </c>
       <c t="s" r="B327" s="7">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c t="s" r="C327" s="7">
         <v>66</v>
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -11608,13 +11713,13 @@
         <v>23</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>84</v>
       </c>
       <c t="s" r="K327" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
@@ -11648,7 +11753,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11660,7 +11765,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>110</v>
@@ -11668,7 +11773,7 @@
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>388</v>
+        <v>397</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -11683,7 +11788,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11695,10 +11800,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11718,7 +11823,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11730,17 +11835,17 @@
         <v>37</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>365</v>
+        <v>156</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="K331" s="7">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -11755,7 +11860,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11767,17 +11872,17 @@
         <v>23</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c t="s" r="K332" s="7">
         <v>60</v>
       </c>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -11792,7 +11897,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11801,13 +11906,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c t="s" r="I333" s="7">
         <v>116</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11825,22 +11930,22 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11858,7 +11963,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11867,13 +11972,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11891,22 +11996,22 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11939,7 +12044,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -11959,7 +12064,7 @@
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -11974,7 +12079,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -11983,17 +12088,19 @@
         <v>37</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c t="s" r="I339" s="7">
         <v>135</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>296</v>
+        <v>159</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
-      <c r="M339" s="7"/>
+      <c t="s" r="M339" s="7">
+        <v>304</v>
+      </c>
     </row>
     <row r="340" ht="15" customHeight="1">
       <c t="s" r="A340" s="6">
@@ -12007,13 +12114,13 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>37</v>
@@ -12040,7 +12147,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -12066,14 +12173,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B342" s="7">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c t="s" r="C342" s="7">
         <v>66</v>
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
@@ -12085,17 +12192,17 @@
         <v>62</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c t="s" r="J342" s="7">
         <v>24</v>
       </c>
       <c t="s" r="K342" s="7">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -12125,7 +12232,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -12134,10 +12241,10 @@
         <v>23</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c t="s" r="J344" s="7">
         <v>109</v>
@@ -12145,7 +12252,7 @@
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>396</v>
+        <v>405</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -12160,13 +12267,13 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c t="s" r="H345" s="8">
         <v>23</v>
@@ -12180,7 +12287,7 @@
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>397</v>
+        <v>406</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -12195,7 +12302,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -12207,14 +12314,16 @@
         <v>98</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
-      <c r="M346" s="7"/>
+      <c t="s" r="M346" s="7">
+        <v>407</v>
+      </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
       <c t="s" r="A347" s="6">
@@ -12228,7 +12337,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12243,7 +12352,7 @@
         <v>60</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12261,7 +12370,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12276,7 +12385,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12294,7 +12403,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12342,7 +12451,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12354,15 +12463,15 @@
         <v>31</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -12377,7 +12486,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12392,11 +12501,13 @@
         <v>76</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
-      <c r="M352" s="7"/>
+      <c t="s" r="M352" s="7">
+        <v>411</v>
+      </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
       <c t="s" r="A353" s="6">
@@ -12410,7 +12521,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12419,10 +12530,10 @@
         <v>95</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>50</v>
@@ -12443,13 +12554,13 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>95</v>
@@ -12458,7 +12569,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12476,7 +12587,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12485,13 +12596,13 @@
         <v>95</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c t="s" r="I355" s="7">
         <v>142</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12509,22 +12620,22 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>95</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12542,7 +12653,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12557,7 +12668,7 @@
         <v>28</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12590,7 +12701,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12602,7 +12713,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>130</v>
@@ -12610,7 +12721,7 @@
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>404</v>
+        <v>415</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -12625,7 +12736,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12660,7 +12771,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12679,7 +12790,9 @@
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
-      <c r="M361" s="7"/>
+      <c t="s" r="M361" s="7">
+        <v>138</v>
+      </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
       <c t="s" r="A362" s="6">
@@ -12693,7 +12806,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12702,7 +12815,7 @@
         <v>94</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="I362" s="7">
         <v>35</v>
@@ -12726,13 +12839,13 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>94</v>
@@ -12741,7 +12854,7 @@
         <v>88</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12759,7 +12872,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12771,10 +12884,10 @@
         <v>98</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12792,7 +12905,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12804,10 +12917,10 @@
         <v>94</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12825,7 +12938,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -12837,10 +12950,10 @@
         <v>73</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12873,7 +12986,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12882,10 +12995,10 @@
         <v>23</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>32</v>
@@ -12893,7 +13006,7 @@
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>408</v>
+        <v>419</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -12908,19 +13021,19 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c t="s" r="H369" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>33</v>
@@ -12930,7 +13043,7 @@
       </c>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>137</v>
+        <v>420</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -12945,7 +13058,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -12957,10 +13070,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12978,7 +13091,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -12990,7 +13103,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c t="s" r="J371" s="7">
         <v>127</v>
@@ -13011,7 +13124,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -13023,10 +13136,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13044,7 +13157,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -13053,13 +13166,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -13077,22 +13190,22 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c t="s" r="H374" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13125,19 +13238,19 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>35</v>
@@ -13145,7 +13258,7 @@
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>409</v>
+        <v>421</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -13160,7 +13273,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13172,10 +13285,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13193,7 +13306,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13205,10 +13318,10 @@
         <v>95</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13226,7 +13339,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -13238,10 +13351,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13274,7 +13387,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13289,14 +13402,14 @@
         <v>111</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c t="s" r="K381" s="7">
         <v>59</v>
       </c>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>47</v>
+        <v>427</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -13311,7 +13424,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13323,10 +13436,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13344,7 +13457,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13356,10 +13469,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13377,7 +13490,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13386,13 +13499,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c t="s" r="I384" s="7">
         <v>24</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13410,22 +13523,22 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>340</v>
+        <v>146</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13458,7 +13571,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13467,10 +13580,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>75</v>
@@ -13478,7 +13591,7 @@
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -13493,27 +13606,27 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>417</v>
+        <v>430</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -13528,7 +13641,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -13543,11 +13656,13 @@
         <v>132</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
-      <c r="M389" s="7"/>
+      <c t="s" r="M389" s="7">
+        <v>431</v>
+      </c>
     </row>
     <row r="390" ht="15" customHeight="1">
       <c t="s" r="A390" s="6">
@@ -13561,7 +13676,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -13573,10 +13688,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>222</v>
+        <v>160</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13594,7 +13709,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -13603,13 +13718,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c t="s" r="I391" s="7">
         <v>99</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13627,22 +13742,22 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13660,7 +13775,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -13669,13 +13784,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c t="s" r="I393" s="7">
         <v>52</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13693,19 +13808,19 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c t="s" r="J394" s="7">
         <v>81</v>
@@ -13741,7 +13856,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -13750,7 +13865,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c t="s" r="I396" s="7">
         <v>18</v>
@@ -13761,7 +13876,7 @@
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>419</v>
+        <v>433</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -13776,22 +13891,22 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c t="s" r="H397" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>222</v>
+        <v>160</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13809,7 +13924,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -13824,7 +13939,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13842,7 +13957,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -13854,10 +13969,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13875,7 +13990,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -13884,13 +13999,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c t="s" r="I400" s="7">
         <v>54</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13908,22 +14023,22 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13956,7 +14071,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -13968,10 +14083,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -14004,7 +14119,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -14016,15 +14131,15 @@
         <v>23</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>425</v>
+        <v>439</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -14039,7 +14154,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -14054,13 +14169,11 @@
         <v>112</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
-      <c t="s" r="M406" s="7">
-        <v>426</v>
-      </c>
+      <c r="M406" s="7"/>
     </row>
     <row r="407" ht="14.25" customHeight="1">
       <c t="s" r="A407" s="6">
@@ -14074,7 +14187,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -14089,7 +14202,7 @@
         <v>126</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -14107,7 +14220,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -14119,10 +14232,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -14140,7 +14253,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -14155,7 +14268,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14173,7 +14286,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -14185,10 +14298,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -14221,7 +14334,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
@@ -14233,7 +14346,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J412" s="7">
         <v>121</v>
@@ -14254,7 +14367,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="F413" s="7">
         <v>330</v>
@@ -14263,7 +14376,7 @@
         <v>74</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c t="s" r="I413" s="7">
         <v>88</v>
@@ -14287,22 +14400,22 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14335,7 +14448,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
@@ -14350,7 +14463,7 @@
         <v>112</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14368,7 +14481,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
@@ -14383,7 +14496,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14416,27 +14529,27 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="F419" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>434</v>
+        <v>447</v>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
@@ -14451,7 +14564,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
@@ -14460,13 +14573,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H420" s="8">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14499,7 +14612,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="F422" s="7">
         <v>330</v>
@@ -14511,14 +14624,16 @@
         <v>74</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J422" s="7">
         <v>150</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
-      <c r="M422" s="7"/>
+      <c t="s" r="M422" s="7">
+        <v>159</v>
+      </c>
     </row>
     <row r="423" ht="14.25" customHeight="1">
       <c t="s" r="A423" s="6">
@@ -14532,7 +14647,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="F423" s="7">
         <v>330</v>
@@ -14544,7 +14659,7 @@
         <v>69</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c t="s" r="J423" s="7">
         <v>128</v>
@@ -14565,7 +14680,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="F424" s="7">
         <v>330</v>
@@ -14577,10 +14692,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -14613,7 +14728,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="F426" s="7">
         <v>330</v>
@@ -14622,7 +14737,7 @@
         <v>74</v>
       </c>
       <c t="s" r="H426" s="8">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c t="s" r="I426" s="7">
         <v>29</v>
@@ -14633,7 +14748,7 @@
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -14648,22 +14763,22 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="F427" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G427" s="8">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c t="s" r="H427" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>438</v>
+        <v>451</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -14696,7 +14811,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="F429" s="7">
         <v>330</v>
@@ -14708,7 +14823,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>296</v>
+        <v>159</v>
       </c>
       <c t="s" r="J429" s="7">
         <v>121</v>
@@ -14729,7 +14844,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
@@ -14738,20 +14853,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H430" s="8">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c t="s" r="K430" s="7">
         <v>36</v>
       </c>
       <c r="L430" s="7"/>
       <c t="s" r="M430" s="7">
-        <v>441</v>
+        <v>454</v>
       </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
@@ -14766,25 +14881,25 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="F431" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G431" s="8">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c t="s" r="H431" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c t="s" r="K431" s="7">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="L431" s="7"/>
       <c t="s" r="M431" s="7">
@@ -14818,7 +14933,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="F433" s="7">
         <v>330</v>
@@ -14827,13 +14942,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H433" s="8">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -14851,22 +14966,22 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="F434" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G434" s="8">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c t="s" r="H434" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -14874,7 +14989,7 @@
     </row>
     <row r="435" ht="16.5" customHeight="1">
       <c t="s" r="A435" s="9">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="B435" s="9"/>
       <c r="C435" s="9"/>
@@ -14894,7 +15009,7 @@
     <row r="436" ht="65.25" customHeight="1"/>
     <row r="437" ht="16.5" customHeight="1">
       <c t="s" r="A437" s="10">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="B437" s="10"/>
       <c r="C437" s="10"/>
@@ -14907,7 +15022,7 @@
       <c r="J437" s="10"/>
       <c r="K437" s="10"/>
       <c t="s" r="L437" s="11">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="M437" s="11"/>
       <c r="N437" s="11"/>

--- a/Data/FlightPlan/FPL_15OCT26.xlsx
+++ b/Data/FlightPlan/FPL_15OCT26.xlsx
@@ -641,6 +641,9 @@
     <t>14:30</t>
   </si>
   <si>
+    <t>14:47</t>
+  </si>
+  <si>
     <t>19:15</t>
   </si>
   <si>
@@ -695,6 +698,9 @@
     <t>08:35</t>
   </si>
   <si>
+    <t>16:51</t>
+  </si>
+  <si>
     <t>17:50</t>
   </si>
   <si>
@@ -959,7 +965,7 @@
     <t>09:14</t>
   </si>
   <si>
-    <t>15:03</t>
+    <t>15:04</t>
   </si>
   <si>
     <t>19:05</t>
@@ -1019,6 +1025,9 @@
     <t>BKK</t>
   </si>
   <si>
+    <t>14:59</t>
+  </si>
+  <si>
     <t>VN-A644</t>
   </si>
   <si>
@@ -1058,6 +1067,9 @@
     <t>13:20</t>
   </si>
   <si>
+    <t>15:21</t>
+  </si>
+  <si>
     <t>00:50</t>
   </si>
   <si>
@@ -1109,225 +1121,228 @@
     <t>11:09</t>
   </si>
   <si>
+    <t>15:22</t>
+  </si>
+  <si>
     <t>17:10</t>
   </si>
   <si>
     <t>19:55</t>
   </si>
   <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>06:39</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>08:49</t>
+  </si>
+  <si>
+    <t>10:41</t>
+  </si>
+  <si>
+    <t>12:46</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>ENH</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>07:49</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>17:27</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>HIJ</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>12:39</t>
+  </si>
+  <si>
+    <t>16:11</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>10:17</t>
+  </si>
+  <si>
+    <t>13:16</t>
+  </si>
+  <si>
+    <t>CMB</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>26 *</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>07:36</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>14:58</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>13:22</t>
+  </si>
+  <si>
+    <t>27 *</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>07:43</t>
+  </si>
+  <si>
+    <t>09:42</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>11:36</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>15:13</t>
+  </si>
+  <si>
     <t>21:55</t>
   </si>
   <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>06:39</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>08:49</t>
-  </si>
-  <si>
-    <t>10:41</t>
-  </si>
-  <si>
-    <t>12:46</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>ENH</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>18:35</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>07:49</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>17:09</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>HIJ</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>12:39</t>
-  </si>
-  <si>
-    <t>16:11</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>10:17</t>
-  </si>
-  <si>
-    <t>13:16</t>
-  </si>
-  <si>
-    <t>CMB</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>26 *</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>07:36</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>14:58</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>13:22</t>
-  </si>
-  <si>
-    <t>27 *</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>07:43</t>
-  </si>
-  <si>
-    <t>09:42</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>11:36</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>15:13</t>
-  </si>
-  <si>
     <t>VN-A683</t>
   </si>
   <si>
@@ -1391,6 +1406,9 @@
     <t>12:23</t>
   </si>
   <si>
+    <t>15:07</t>
+  </si>
+  <si>
     <t>VN-A693</t>
   </si>
   <si>
@@ -1400,7 +1418,7 @@
     <t>11:49</t>
   </si>
   <si>
-    <t>14:56</t>
+    <t>15:12</t>
   </si>
   <si>
     <t>BOM</t>
@@ -1430,6 +1448,9 @@
     <t>KJA</t>
   </si>
   <si>
+    <t>20:56</t>
+  </si>
+  <si>
     <t>05:50</t>
   </si>
   <si>
@@ -1490,7 +1511,7 @@
     <t>Total Record(s): 354</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 15, 2026 13:17</t>
+    <t xml:space="preserve">Generated on  Oct 15, 2026 13:50</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3355,7 +3376,9 @@
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
-      <c r="M50" s="7"/>
+      <c t="s" r="M50" s="7">
+        <v>38</v>
+      </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="6"/>
@@ -4888,7 +4911,9 @@
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
-      <c r="M99" s="7"/>
+      <c t="s" r="M99" s="7">
+        <v>210</v>
+      </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c t="s" r="A100" s="6">
@@ -4917,7 +4942,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4950,7 +4975,7 @@
         <v>191</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4983,7 +5008,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4995,7 +5020,7 @@
         <v>155</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J103" s="7">
         <v>137</v>
@@ -5003,7 +5028,7 @@
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
       <c t="s" r="M103" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
@@ -5018,7 +5043,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5033,12 +5058,12 @@
         <v>140</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c t="s" r="M104" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -5053,7 +5078,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -5073,7 +5098,7 @@
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
       <c t="s" r="M105" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
@@ -5088,7 +5113,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5136,7 +5161,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5156,7 +5181,7 @@
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
       <c t="s" r="M108" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -5171,7 +5196,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5183,7 +5208,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J109" s="7">
         <v>38</v>
@@ -5208,7 +5233,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5217,7 +5242,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H110" s="8">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="I110" s="7">
         <v>21</v>
@@ -5226,7 +5251,7 @@
         <v>41</v>
       </c>
       <c t="s" r="K110" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L110" s="7"/>
       <c t="s" r="M110" s="7">
@@ -5245,13 +5270,13 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G111" s="8">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="H111" s="8">
         <v>16</v>
@@ -5263,11 +5288,11 @@
         <v>43</v>
       </c>
       <c t="s" r="K111" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5282,7 +5307,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5294,10 +5319,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -5315,7 +5340,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5327,7 +5352,7 @@
         <v>128</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J113" s="7">
         <v>31</v>
@@ -5363,7 +5388,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5375,7 +5400,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J115" s="7">
         <v>114</v>
@@ -5398,7 +5423,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5410,7 +5435,7 @@
         <v>93</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J116" s="7">
         <v>20</v>
@@ -5433,7 +5458,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5452,7 +5477,9 @@
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
-      <c r="M117" s="7"/>
+      <c t="s" r="M117" s="7">
+        <v>229</v>
+      </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
       <c t="s" r="A118" s="6">
@@ -5466,7 +5493,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5478,7 +5505,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J118" s="7">
         <v>132</v>
@@ -5499,7 +5526,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5511,10 +5538,10 @@
         <v>77</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5547,7 +5574,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5559,15 +5586,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
       <c t="s" r="M121" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -5582,7 +5609,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5591,10 +5618,10 @@
         <v>33</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>83</v>
@@ -5602,7 +5629,7 @@
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
       <c t="s" r="M122" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -5617,13 +5644,13 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>33</v>
@@ -5632,7 +5659,7 @@
         <v>106</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5650,7 +5677,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5683,7 +5710,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5695,10 +5722,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5731,7 +5758,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5766,7 +5793,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5781,7 +5808,7 @@
         <v>130</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5799,7 +5826,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5811,7 +5838,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c t="s" r="J129" s="7">
         <v>26</v>
@@ -5832,7 +5859,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5865,7 +5892,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5877,7 +5904,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J131" s="7">
         <v>162</v>
@@ -5913,19 +5940,19 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="H133" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="J133" s="7">
         <v>144</v>
@@ -5933,7 +5960,7 @@
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
@@ -5948,7 +5975,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5963,11 +5990,13 @@
         <v>100</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
-      <c r="M134" s="7"/>
+      <c t="s" r="M134" s="7">
+        <v>121</v>
+      </c>
     </row>
     <row r="135" ht="15" customHeight="1">
       <c t="s" r="A135" s="6">
@@ -5981,7 +6010,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5993,7 +6022,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J135" s="7">
         <v>60</v>
@@ -6014,7 +6043,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6026,7 +6055,7 @@
         <v>111</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>31</v>
@@ -6062,7 +6091,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -6082,7 +6111,7 @@
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
       <c t="s" r="M138" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -6097,7 +6126,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6109,10 +6138,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -6130,7 +6159,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6139,7 +6168,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="I140" s="7">
         <v>191</v>
@@ -6163,22 +6192,22 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -6211,7 +6240,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6229,7 +6258,7 @@
         <v>143</v>
       </c>
       <c t="s" r="K143" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
@@ -6248,7 +6277,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6281,7 +6310,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6296,7 +6325,7 @@
         <v>74</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -6314,7 +6343,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6326,7 +6355,7 @@
         <v>44</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="J146" s="7">
         <v>124</v>
@@ -6362,13 +6391,13 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>16</v>
@@ -6377,12 +6406,12 @@
         <v>141</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6397,7 +6426,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6430,7 +6459,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6445,7 +6474,7 @@
         <v>27</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6463,7 +6492,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6472,13 +6501,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H151" s="8">
+        <v>262</v>
+      </c>
+      <c t="s" r="I151" s="7">
         <v>260</v>
       </c>
-      <c t="s" r="I151" s="7">
+      <c t="s" r="J151" s="7">
         <v>258</v>
-      </c>
-      <c t="s" r="J151" s="7">
-        <v>256</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6511,7 +6540,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6546,7 +6575,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6558,10 +6587,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6579,7 +6608,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6627,7 +6656,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6639,7 +6668,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="J157" s="7">
         <v>37</v>
@@ -6647,7 +6676,7 @@
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -6662,7 +6691,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6674,7 +6703,7 @@
         <v>98</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="J158" s="7">
         <v>64</v>
@@ -6697,7 +6726,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6730,7 +6759,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6742,7 +6771,7 @@
         <v>98</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J160" s="7">
         <v>148</v>
@@ -6763,7 +6792,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6772,13 +6801,13 @@
         <v>98</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6796,22 +6825,22 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="H162" s="8">
         <v>98</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6844,7 +6873,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6864,7 +6893,7 @@
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -6879,7 +6908,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6894,12 +6923,12 @@
         <v>175</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -6914,7 +6943,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6934,7 +6963,7 @@
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -6949,7 +6978,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6964,7 +6993,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6982,7 +7011,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6997,7 +7026,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -7015,7 +7044,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7048,7 +7077,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7096,7 +7125,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7111,7 +7140,7 @@
         <v>195</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -7131,7 +7160,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7143,7 +7172,7 @@
         <v>98</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c t="s" r="J173" s="7">
         <v>20</v>
@@ -7166,7 +7195,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7181,7 +7210,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -7199,7 +7228,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7211,7 +7240,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c t="s" r="J175" s="7">
         <v>147</v>
@@ -7232,7 +7261,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7247,7 +7276,7 @@
         <v>132</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7265,7 +7294,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7277,10 +7306,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7298,7 +7327,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7310,10 +7339,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7346,7 +7375,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7366,7 +7395,7 @@
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7381,7 +7410,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7396,12 +7425,12 @@
         <v>140</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7416,7 +7445,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7428,17 +7457,17 @@
         <v>98</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c t="s" r="K182" s="7">
         <v>99</v>
       </c>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7453,7 +7482,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7468,7 +7497,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="K183" s="7">
         <v>130</v>
@@ -7490,7 +7519,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7508,11 +7537,11 @@
         <v>133</v>
       </c>
       <c t="s" r="K184" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L184" s="7"/>
       <c t="s" r="M184" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
@@ -7527,7 +7556,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7549,7 +7578,7 @@
       </c>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -7564,7 +7593,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7576,10 +7605,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7612,7 +7641,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7621,10 +7650,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c t="s" r="J188" s="7">
         <v>115</v>
@@ -7632,7 +7661,7 @@
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -7647,13 +7676,13 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c t="s" r="H189" s="8">
         <v>16</v>
@@ -7662,12 +7691,12 @@
         <v>198</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -7682,7 +7711,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7694,7 +7723,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J190" s="7">
         <v>144</v>
@@ -7702,7 +7731,7 @@
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -7717,7 +7746,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7737,7 +7766,7 @@
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -7752,7 +7781,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7785,7 +7814,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7818,7 +7847,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7827,13 +7856,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7851,22 +7880,22 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="H195" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7899,7 +7928,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7908,18 +7937,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="I197" s="7">
         <v>63</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -7934,13 +7963,13 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>16</v>
@@ -7949,12 +7978,12 @@
         <v>92</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -7969,7 +7998,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7984,7 +8013,7 @@
         <v>188</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -8002,7 +8031,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8050,7 +8079,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8065,12 +8094,12 @@
         <v>79</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8085,7 +8114,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8105,7 +8134,7 @@
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8120,7 +8149,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8140,7 +8169,7 @@
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8155,7 +8184,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8170,7 +8199,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -8188,7 +8217,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8203,7 +8232,7 @@
         <v>146</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -8221,7 +8250,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8233,7 +8262,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="J207" s="7">
         <v>95</v>
@@ -8254,7 +8283,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8269,7 +8298,7 @@
         <v>172</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -8287,7 +8316,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8299,10 +8328,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -8335,7 +8364,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8355,7 +8384,7 @@
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8370,7 +8399,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8390,7 +8419,7 @@
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
       <c t="s" r="M212" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
@@ -8405,7 +8434,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8425,7 +8454,7 @@
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -8440,7 +8469,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8452,17 +8481,17 @@
         <v>139</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>179</v>
       </c>
       <c t="s" r="K214" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8477,7 +8506,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8529,7 +8558,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8544,7 +8573,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8577,7 +8606,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8586,10 +8615,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="J219" s="7">
         <v>46</v>
@@ -8597,7 +8626,7 @@
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -8612,19 +8641,19 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="H220" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c t="s" r="J220" s="7">
         <v>63</v>
@@ -8632,7 +8661,7 @@
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -8647,7 +8676,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8667,7 +8696,7 @@
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -8682,7 +8711,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8697,7 +8726,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8715,7 +8744,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8724,13 +8753,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8748,13 +8777,13 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>16</v>
@@ -8781,7 +8810,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8793,10 +8822,10 @@
         <v>97</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8814,7 +8843,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8826,10 +8855,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8862,7 +8891,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8871,17 +8900,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c t="s" r="I228" s="7">
         <v>101</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
-      <c r="M228" s="7"/>
+      <c t="s" r="M228" s="7">
+        <v>338</v>
+      </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
       <c t="s" r="A229" s="6">
@@ -8895,13 +8926,13 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>16</v>
@@ -8910,7 +8941,7 @@
         <v>179</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8928,7 +8959,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8961,7 +8992,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9009,7 +9040,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9024,12 +9055,12 @@
         <v>49</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -9044,7 +9075,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9053,10 +9084,10 @@
         <v>23</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>64</v>
@@ -9064,7 +9095,7 @@
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -9079,13 +9110,13 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>23</v>
@@ -9112,7 +9143,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9145,7 +9176,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9160,7 +9191,7 @@
         <v>170</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -9178,7 +9209,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9187,7 +9218,7 @@
         <v>23</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c t="s" r="I238" s="7">
         <v>123</v>
@@ -9226,7 +9257,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9238,7 +9269,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>19</v>
@@ -9261,7 +9292,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9273,7 +9304,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="J241" s="7">
         <v>18</v>
@@ -9309,7 +9340,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9321,7 +9352,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c t="s" r="J243" s="7">
         <v>113</v>
@@ -9329,7 +9360,7 @@
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -9344,7 +9375,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9359,7 +9390,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9379,7 +9410,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9394,11 +9425,13 @@
         <v>38</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
-      <c r="M245" s="7"/>
+      <c t="s" r="M245" s="7">
+        <v>22</v>
+      </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
       <c t="s" r="A246" s="6">
@@ -9412,7 +9445,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9460,7 +9493,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9475,12 +9508,12 @@
         <v>115</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -9495,7 +9528,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9507,7 +9540,7 @@
         <v>98</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>38</v>
@@ -9515,7 +9548,7 @@
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -9530,7 +9563,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9547,9 +9580,13 @@
       <c t="s" r="J250" s="7">
         <v>105</v>
       </c>
-      <c r="K250" s="7"/>
+      <c t="s" r="K250" s="7">
+        <v>281</v>
+      </c>
       <c r="L250" s="7"/>
-      <c r="M250" s="7"/>
+      <c t="s" r="M250" s="7">
+        <v>121</v>
+      </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
       <c t="s" r="A251" s="6">
@@ -9563,7 +9600,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9575,14 +9612,18 @@
         <v>78</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>228</v>
-      </c>
-      <c r="K251" s="7"/>
+        <v>230</v>
+      </c>
+      <c t="s" r="K251" s="7">
+        <v>42</v>
+      </c>
       <c r="L251" s="7"/>
-      <c r="M251" s="7"/>
+      <c t="s" r="M251" s="7">
+        <v>43</v>
+      </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
       <c t="s" r="A252" s="6">
@@ -9596,7 +9637,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9613,9 +9654,13 @@
       <c t="s" r="J252" s="7">
         <v>27</v>
       </c>
-      <c r="K252" s="7"/>
+      <c t="s" r="K252" s="7">
+        <v>158</v>
+      </c>
       <c r="L252" s="7"/>
-      <c r="M252" s="7"/>
+      <c t="s" r="M252" s="7">
+        <v>107</v>
+      </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
       <c t="s" r="A253" s="6">
@@ -9629,7 +9674,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9641,7 +9686,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J253" s="7">
         <v>18</v>
@@ -9677,7 +9722,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9689,14 +9734,16 @@
         <v>23</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
-      <c r="M255" s="7"/>
+      <c t="s" r="M255" s="7">
+        <v>352</v>
+      </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
       <c t="s" r="A256" s="6">
@@ -9710,7 +9757,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9722,10 +9769,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9743,7 +9790,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9755,10 +9802,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9791,7 +9838,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F259" s="7">
         <v>320</v>
@@ -9803,15 +9850,15 @@
         <v>23</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -9826,7 +9873,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F260" s="7">
         <v>320</v>
@@ -9846,7 +9893,7 @@
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -9861,7 +9908,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F261" s="7">
         <v>320</v>
@@ -9870,18 +9917,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c t="s" r="I261" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -9896,22 +9943,22 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F262" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9929,7 +9976,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F263" s="7">
         <v>320</v>
@@ -9938,10 +9985,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>146</v>
@@ -9962,13 +10009,13 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>16</v>
@@ -10010,7 +10057,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -10019,10 +10066,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c t="s" r="J266" s="7">
         <v>80</v>
@@ -10030,7 +10077,7 @@
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10045,27 +10092,27 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10080,7 +10127,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -10100,7 +10147,7 @@
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
-        <v>220</v>
+        <v>370</v>
       </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
@@ -10115,7 +10162,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -10127,17 +10174,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c t="s" r="K269" s="7">
-        <v>121</v>
+        <v>297</v>
       </c>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>228</v>
+        <v>43</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10152,7 +10199,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10170,11 +10217,11 @@
         <v>199</v>
       </c>
       <c t="s" r="K270" s="7">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>367</v>
+        <v>298</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10189,7 +10236,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10201,17 +10248,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>152</v>
       </c>
       <c t="s" r="K271" s="7">
-        <v>286</v>
+        <v>160</v>
       </c>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>368</v>
+        <v>223</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10241,7 +10288,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10250,13 +10297,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -10274,22 +10321,22 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -10322,7 +10369,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
@@ -10337,12 +10384,12 @@
         <v>135</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
@@ -10357,7 +10404,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
@@ -10369,10 +10416,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10385,14 +10432,14 @@
         <v>13</v>
       </c>
       <c r="B278" s="7">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c t="s" r="C278" s="7">
         <v>14</v>
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
@@ -10401,13 +10448,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>313</v>
+        <v>244</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10418,29 +10465,29 @@
         <v>13</v>
       </c>
       <c r="B279" s="7">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c t="s" r="C279" s="7">
         <v>14</v>
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>146</v>
+        <v>371</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>199</v>
+        <v>158</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10458,7 +10505,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -10473,7 +10520,7 @@
         <v>27</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10506,7 +10553,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10515,18 +10562,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="I282" s="7">
         <v>194</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -10541,19 +10588,19 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>206</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>34</v>
@@ -10561,7 +10608,7 @@
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -10576,7 +10623,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10585,18 +10632,18 @@
         <v>206</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -10611,19 +10658,19 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>64</v>
@@ -10631,7 +10678,7 @@
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -10646,7 +10693,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10679,7 +10726,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10691,7 +10738,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>43</v>
@@ -10712,7 +10759,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10745,7 +10792,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10757,10 +10804,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10793,13 +10840,13 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c t="s" r="H291" s="8">
         <v>23</v>
@@ -10828,7 +10875,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -10837,20 +10884,20 @@
         <v>23</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c t="s" r="I292" s="7">
         <v>21</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c t="s" r="K292" s="7">
         <v>53</v>
       </c>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -10865,13 +10912,13 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>23</v>
@@ -10883,11 +10930,11 @@
         <v>199</v>
       </c>
       <c t="s" r="K293" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -10902,7 +10949,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10911,13 +10958,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c t="s" r="I294" s="7">
         <v>200</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10935,22 +10982,22 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10983,7 +11030,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
@@ -10995,7 +11042,7 @@
         <v>97</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c t="s" r="J297" s="7">
         <v>49</v>
@@ -11003,7 +11050,7 @@
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11018,7 +11065,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -11033,7 +11080,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -11053,7 +11100,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -11065,7 +11112,7 @@
         <v>98</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>176</v>
@@ -11075,7 +11122,7 @@
       </c>
       <c r="L299" s="7"/>
       <c t="s" r="M299" s="7">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1">
@@ -11090,7 +11137,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -11110,7 +11157,7 @@
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -11125,7 +11172,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -11137,7 +11184,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>74</v>
@@ -11158,22 +11205,22 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
+        <v>396</v>
+      </c>
+      <c r="F302" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G302" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H302" s="8">
         <v>392</v>
       </c>
-      <c r="F302" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G302" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H302" s="8">
-        <v>388</v>
-      </c>
       <c t="s" r="I302" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -11191,22 +11238,22 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
+        <v>396</v>
+      </c>
+      <c r="F303" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G303" s="8">
         <v>392</v>
       </c>
-      <c r="F303" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G303" s="8">
-        <v>388</v>
-      </c>
       <c t="s" r="H303" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -11239,7 +11286,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -11248,18 +11295,18 @@
         <v>23</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11274,13 +11321,13 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>23</v>
@@ -11289,12 +11336,12 @@
         <v>38</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11309,7 +11356,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -11342,7 +11389,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11357,7 +11404,7 @@
         <v>150</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -11390,7 +11437,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -11402,15 +11449,15 @@
         <v>23</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11425,7 +11472,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -11440,12 +11487,12 @@
         <v>80</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11460,7 +11507,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -11475,7 +11522,7 @@
         <v>104</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11493,7 +11540,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11508,7 +11555,7 @@
         <v>132</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11541,7 +11588,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11553,7 +11600,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J315" s="7">
         <v>38</v>
@@ -11576,7 +11623,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11591,14 +11638,14 @@
         <v>209</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c t="s" r="K316" s="7">
         <v>53</v>
       </c>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -11613,7 +11660,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11622,7 +11669,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c t="s" r="I317" s="7">
         <v>189</v>
@@ -11646,13 +11693,13 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>16</v>
@@ -11694,7 +11741,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11703,18 +11750,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -11729,13 +11776,13 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>16</v>
@@ -11749,7 +11796,7 @@
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -11764,7 +11811,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11776,10 +11823,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11797,7 +11844,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11809,7 +11856,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>106</v>
@@ -11830,7 +11877,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11839,13 +11886,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c t="s" r="I324" s="7">
         <v>148</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11863,19 +11910,19 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>192</v>
@@ -11904,14 +11951,14 @@
         <v>28</v>
       </c>
       <c t="s" r="B327" s="7">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c t="s" r="C327" s="7">
         <v>70</v>
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -11923,7 +11970,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>88</v>
@@ -11963,7 +12010,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11975,7 +12022,7 @@
         <v>78</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>114</v>
@@ -11983,7 +12030,7 @@
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -11998,7 +12045,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -12010,7 +12057,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c t="s" r="J330" s="7">
         <v>163</v>
@@ -12033,7 +12080,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -12051,7 +12098,7 @@
         <v>207</v>
       </c>
       <c t="s" r="K331" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
@@ -12070,7 +12117,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -12085,14 +12132,14 @@
         <v>145</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c t="s" r="K332" s="7">
         <v>64</v>
       </c>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12100,14 +12147,14 @@
         <v>13</v>
       </c>
       <c r="B333" s="7">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c t="s" r="C333" s="7">
         <v>14</v>
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -12116,13 +12163,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>242</v>
+        <v>315</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -12133,29 +12180,29 @@
         <v>13</v>
       </c>
       <c r="B334" s="7">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c t="s" r="C334" s="7">
         <v>14</v>
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>366</v>
+        <v>146</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>158</v>
+        <v>199</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -12173,7 +12220,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -12182,17 +12229,21 @@
         <v>23</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>425</v>
-      </c>
-      <c r="K335" s="7"/>
+        <v>429</v>
+      </c>
+      <c t="s" r="K335" s="7">
+        <v>84</v>
+      </c>
       <c r="L335" s="7"/>
-      <c r="M335" s="7"/>
+      <c t="s" r="M335" s="7">
+        <v>335</v>
+      </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
       <c t="s" r="A336" s="6">
@@ -12206,13 +12257,13 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>23</v>
@@ -12221,11 +12272,15 @@
         <v>45</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>426</v>
-      </c>
-      <c r="K336" s="7"/>
+        <v>430</v>
+      </c>
+      <c t="s" r="K336" s="7">
+        <v>291</v>
+      </c>
       <c r="L336" s="7"/>
-      <c r="M336" s="7"/>
+      <c t="s" r="M336" s="7">
+        <v>186</v>
+      </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
       <c r="A337" s="6"/>
@@ -12254,7 +12309,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -12289,7 +12344,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -12298,7 +12353,7 @@
         <v>40</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="I339" s="7">
         <v>140</v>
@@ -12309,7 +12364,7 @@
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12324,13 +12379,13 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>40</v>
@@ -12344,7 +12399,7 @@
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12359,7 +12414,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -12385,14 +12440,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B342" s="7">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c t="s" r="C342" s="7">
         <v>70</v>
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
@@ -12404,17 +12459,17 @@
         <v>66</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J342" s="7">
         <v>24</v>
       </c>
       <c t="s" r="K342" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -12444,7 +12499,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -12453,10 +12508,10 @@
         <v>23</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c t="s" r="J344" s="7">
         <v>113</v>
@@ -12464,7 +12519,7 @@
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -12479,13 +12534,13 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c t="s" r="H345" s="8">
         <v>23</v>
@@ -12499,7 +12554,7 @@
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -12514,7 +12569,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -12526,15 +12581,15 @@
         <v>102</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -12549,7 +12604,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12564,7 +12619,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12584,7 +12639,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12599,7 +12654,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12617,7 +12672,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12665,7 +12720,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12677,7 +12732,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>175</v>
@@ -12685,7 +12740,7 @@
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -12700,7 +12755,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12715,12 +12770,12 @@
         <v>80</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -12735,7 +12790,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12744,7 +12799,7 @@
         <v>98</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c t="s" r="I353" s="7">
         <v>207</v>
@@ -12755,7 +12810,7 @@
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -12770,13 +12825,13 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>98</v>
@@ -12785,7 +12840,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12803,7 +12858,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12812,7 +12867,7 @@
         <v>98</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c t="s" r="I355" s="7">
         <v>148</v>
@@ -12836,22 +12891,22 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>98</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>368</v>
+        <v>443</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12869,7 +12924,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12884,7 +12939,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12917,7 +12972,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12929,7 +12984,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>135</v>
@@ -12937,7 +12992,7 @@
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -12952,7 +13007,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12987,7 +13042,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -13022,7 +13077,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13042,7 +13097,7 @@
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13057,7 +13112,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13090,7 +13145,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -13105,7 +13160,7 @@
         <v>179</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -13123,7 +13178,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -13138,7 +13193,7 @@
         <v>147</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -13156,7 +13211,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -13168,10 +13223,10 @@
         <v>77</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -13204,7 +13259,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -13213,7 +13268,7 @@
         <v>23</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="I368" s="7">
         <v>195</v>
@@ -13224,7 +13279,7 @@
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13239,19 +13294,19 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="H369" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>35</v>
@@ -13261,7 +13316,7 @@
       </c>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13276,7 +13331,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13288,15 +13343,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13311,7 +13366,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -13323,7 +13378,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="J371" s="7">
         <v>131</v>
@@ -13344,7 +13399,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -13359,7 +13414,7 @@
         <v>170</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13377,7 +13432,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -13386,13 +13441,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="I373" s="7">
         <v>151</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -13410,22 +13465,22 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="H374" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13458,19 +13513,19 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>37</v>
@@ -13493,7 +13548,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13513,7 +13568,7 @@
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -13528,7 +13583,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13540,14 +13595,18 @@
         <v>98</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>269</v>
-      </c>
-      <c r="K378" s="7"/>
+        <v>271</v>
+      </c>
+      <c t="s" r="K378" s="7">
+        <v>105</v>
+      </c>
       <c r="L378" s="7"/>
-      <c r="M378" s="7"/>
+      <c t="s" r="M378" s="7">
+        <v>131</v>
+      </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
       <c t="s" r="A379" s="6">
@@ -13561,7 +13620,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -13573,14 +13632,18 @@
         <v>16</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c t="s" r="J379" s="7">
         <v>180</v>
       </c>
-      <c r="K379" s="7"/>
+      <c t="s" r="K379" s="7">
+        <v>286</v>
+      </c>
       <c r="L379" s="7"/>
-      <c r="M379" s="7"/>
+      <c t="s" r="M379" s="7">
+        <v>158</v>
+      </c>
     </row>
     <row r="380" ht="15" customHeight="1">
       <c r="A380" s="6"/>
@@ -13609,7 +13672,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13624,14 +13687,14 @@
         <v>115</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="K381" s="7">
         <v>63</v>
       </c>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -13646,7 +13709,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13658,10 +13721,10 @@
         <v>78</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13679,7 +13742,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13691,10 +13754,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13712,7 +13775,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13721,13 +13784,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c t="s" r="I384" s="7">
         <v>24</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="K384" s="7">
         <v>189</v>
@@ -13749,13 +13812,13 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>16</v>
@@ -13767,11 +13830,11 @@
         <v>152</v>
       </c>
       <c t="s" r="K385" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -13801,7 +13864,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13810,10 +13873,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>79</v>
@@ -13821,7 +13884,7 @@
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -13836,27 +13899,27 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -13871,7 +13934,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -13886,12 +13949,12 @@
         <v>137</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -13906,7 +13969,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -13918,15 +13981,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -13941,7 +14004,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -13950,7 +14013,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="I391" s="7">
         <v>103</v>
@@ -13960,7 +14023,9 @@
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
-      <c r="M391" s="7"/>
+      <c t="s" r="M391" s="7">
+        <v>465</v>
+      </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
       <c t="s" r="A392" s="6">
@@ -13974,13 +14039,13 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>16</v>
@@ -13989,7 +14054,7 @@
         <v>179</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -14007,7 +14072,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -14016,7 +14081,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c t="s" r="I393" s="7">
         <v>56</v>
@@ -14040,19 +14105,19 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="J394" s="7">
         <v>85</v>
@@ -14088,7 +14153,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -14097,7 +14162,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="I396" s="7">
         <v>18</v>
@@ -14108,7 +14173,7 @@
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -14123,27 +14188,27 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="H397" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14158,7 +14223,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -14178,7 +14243,7 @@
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -14193,7 +14258,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -14208,7 +14273,7 @@
         <v>179</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -14226,7 +14291,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -14235,13 +14300,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c t="s" r="I400" s="7">
         <v>58</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -14259,22 +14324,22 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -14307,7 +14372,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -14319,10 +14384,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -14355,7 +14420,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -14367,7 +14432,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J405" s="7">
         <v>175</v>
@@ -14375,7 +14440,7 @@
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -14390,7 +14455,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -14410,7 +14475,7 @@
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14425,7 +14490,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -14440,7 +14505,7 @@
         <v>130</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -14458,7 +14523,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -14470,10 +14535,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -14491,7 +14556,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -14524,7 +14589,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -14536,10 +14601,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -14572,7 +14637,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
@@ -14607,7 +14672,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="F413" s="7">
         <v>330</v>
@@ -14616,7 +14681,7 @@
         <v>78</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c t="s" r="I413" s="7">
         <v>92</v>
@@ -14626,7 +14691,9 @@
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
-      <c r="M413" s="7"/>
+      <c t="s" r="M413" s="7">
+        <v>479</v>
+      </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
       <c t="s" r="A414" s="6">
@@ -14640,22 +14707,22 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>78</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14688,7 +14755,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
@@ -14708,7 +14775,7 @@
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>475</v>
+        <v>482</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -14723,7 +14790,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
@@ -14738,7 +14805,7 @@
         <v>74</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14771,27 +14838,27 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="F419" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>478</v>
+        <v>485</v>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
@@ -14806,7 +14873,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
@@ -14815,13 +14882,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H420" s="8">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14854,7 +14921,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="F422" s="7">
         <v>330</v>
@@ -14866,7 +14933,7 @@
         <v>78</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="J422" s="7">
         <v>156</v>
@@ -14889,7 +14956,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="F423" s="7">
         <v>330</v>
@@ -14901,7 +14968,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c t="s" r="J423" s="7">
         <v>132</v>
@@ -14909,7 +14976,7 @@
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>480</v>
+        <v>487</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -14924,7 +14991,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="F424" s="7">
         <v>330</v>
@@ -14936,10 +15003,10 @@
         <v>78</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -14972,7 +15039,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="F426" s="7">
         <v>330</v>
@@ -14981,7 +15048,7 @@
         <v>78</v>
       </c>
       <c t="s" r="H426" s="8">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c t="s" r="I426" s="7">
         <v>31</v>
@@ -14992,7 +15059,7 @@
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -15007,22 +15074,22 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="F427" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G427" s="8">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c t="s" r="H427" s="8">
         <v>78</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -15055,7 +15122,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="F429" s="7">
         <v>330</v>
@@ -15075,7 +15142,7 @@
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
       <c t="s" r="M429" s="7">
-        <v>485</v>
+        <v>492</v>
       </c>
     </row>
     <row r="430" ht="15" customHeight="1">
@@ -15090,7 +15157,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
@@ -15099,20 +15166,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H430" s="8">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="K430" s="7">
         <v>38</v>
       </c>
       <c r="L430" s="7"/>
       <c t="s" r="M430" s="7">
-        <v>487</v>
+        <v>494</v>
       </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
@@ -15127,13 +15194,13 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="F431" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G431" s="8">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c t="s" r="H431" s="8">
         <v>16</v>
@@ -15142,10 +15209,10 @@
         <v>184</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c t="s" r="K431" s="7">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="L431" s="7"/>
       <c t="s" r="M431" s="7">
@@ -15179,7 +15246,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="F433" s="7">
         <v>330</v>
@@ -15188,18 +15255,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H433" s="8">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
       <c t="s" r="M433" s="7">
-        <v>490</v>
+        <v>497</v>
       </c>
     </row>
     <row r="434" ht="14.25" customHeight="1">
@@ -15214,19 +15281,19 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="F434" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G434" s="8">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c t="s" r="H434" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c t="s" r="J434" s="7">
         <v>194</v>
@@ -15237,7 +15304,7 @@
     </row>
     <row r="435" ht="16.5" customHeight="1">
       <c t="s" r="A435" s="9">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="B435" s="9"/>
       <c r="C435" s="9"/>
@@ -15257,7 +15324,7 @@
     <row r="436" ht="65.25" customHeight="1"/>
     <row r="437" ht="16.5" customHeight="1">
       <c t="s" r="A437" s="10">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="B437" s="10"/>
       <c r="C437" s="10"/>
@@ -15270,7 +15337,7 @@
       <c r="J437" s="10"/>
       <c r="K437" s="10"/>
       <c t="s" r="L437" s="11">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="M437" s="11"/>
       <c r="N437" s="11"/>
